--- a/data/Caboodle_Backlog_by_Module (1).xlsx
+++ b/data/Caboodle_Backlog_by_Module (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tauhid-Aitpc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\My Code\Caboodle\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF531D16-979B-423B-B1C4-2C8FFCDA489C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F34D0CE-F834-454D-BE04-D1A6C803F118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5985" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6024" uniqueCount="957">
   <si>
     <t>Caboodle — Jira Backlog Organized by Module</t>
   </si>
@@ -3004,12 +3004,429 @@
   <si>
     <t>6d</t>
   </si>
+  <si>
+    <t>CR1</t>
+  </si>
+  <si>
+    <t>BD1</t>
+  </si>
+  <si>
+    <t>BD2</t>
+  </si>
+  <si>
+    <t>BD3</t>
+  </si>
+  <si>
+    <t>BD4</t>
+  </si>
+  <si>
+    <t>CR4</t>
+  </si>
+  <si>
+    <t>CR5</t>
+  </si>
+  <si>
+    <t>Both are typed Question (rather than User Story) since they're explicitly open questions, and both link to the relevant existing tickets (CS-1296, CS-1316, CS-1361, CR4). Not yet committed.</t>
+  </si>
+  <si>
+    <t>PM7 (BUG)</t>
+  </si>
+  <si>
+    <t>BMP1</t>
+  </si>
+  <si>
+    <t>BMP2</t>
+  </si>
+  <si>
+    <t>BMTSS1</t>
+  </si>
+  <si>
+    <t>BMTSS2</t>
+  </si>
+  <si>
+    <t>BMTSS3</t>
+  </si>
+  <si>
+    <t>BMTSS4</t>
+  </si>
+  <si>
+    <t>BMTSS5</t>
+  </si>
+  <si>
+    <t>BMTSS6</t>
+  </si>
+  <si>
+    <r>
+      <t>Important findings before writing — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>data/jira-tickets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t> shows strong overlap:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BMTSS3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (EDLP stepper vs edit details) → directly matches </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1302</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> ("determine if this should be added in the Promo Results Page … or Step 4 Metrics in the stepper").</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BMTSS4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (Actualize) → there's </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>already a working file</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>CS-NEW-brand-tss-actualize-promotions.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>tickets/trade-spend/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, plus Jira </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1280</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (Actuals Auto Updated from Distributor Reports), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1283</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1335</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BMTSS6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (EDLP only in Jan) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>exact match</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> with Jira </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1436</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> ("EDLP Promotional Reporting only Populating the Month of January … works in Broker Promotional Management … same in Monthly Report").</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BMTSS1/BMTSS2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (remove/modify approved) → related to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1122</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (copy-to-approved SOP, cancelled-event indication), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1208</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (can't rename in BAP), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1183</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (TSS↔BAP inconsistency), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1160</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BMTSS5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (promo details spacing) → context cluster </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>CS-1188/CS-1239/CS-827</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (Edit Promo Event Details).</t>
+    </r>
+  </si>
+  <si>
+    <t>BMTPS1</t>
+  </si>
+  <si>
+    <t>BMTRC1</t>
+  </si>
+  <si>
+    <t>ACDU1</t>
+  </si>
+  <si>
+    <t>AD1</t>
+  </si>
+  <si>
+    <t>AAC1</t>
+  </si>
+  <si>
+    <t>AAC2</t>
+  </si>
+  <si>
+    <t>ANAWT1</t>
+  </si>
+  <si>
+    <t>ASR1</t>
+  </si>
+  <si>
+    <t>RDR1</t>
+  </si>
+  <si>
+    <t>RDR2</t>
+  </si>
+  <si>
+    <t>RBMO1</t>
+  </si>
+  <si>
+    <t>RBMO2</t>
+  </si>
+  <si>
+    <t>RBS1</t>
+  </si>
+  <si>
+    <t>RBST1</t>
+  </si>
+  <si>
+    <r>
+      <t>SRM1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3155,8 +3572,54 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3283,8 +3746,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3440,12 +3908,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3712,31 +4190,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3783,8 +4246,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Accent2" xfId="2" builtinId="33"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3941,9 +4438,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1047825</xdr:colOff>
+      <xdr:colOff>1044015</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>97215</xdr:rowOff>
+      <xdr:rowOff>93405</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3985,7 +4482,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>16252</xdr:colOff>
+      <xdr:colOff>20062</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>379094</xdr:rowOff>
     </xdr:to>
@@ -4031,7 +4528,7 @@
       <xdr:col>34</xdr:col>
       <xdr:colOff>532286</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>288836</xdr:rowOff>
+      <xdr:rowOff>285026</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4429,197 +4926,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
     </row>
     <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="114" t="s">
+      <c r="B3" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
     </row>
     <row r="4" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="114"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="114"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
     </row>
     <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="137" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
     </row>
     <row r="8" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="114" t="s">
+      <c r="B8" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
     </row>
     <row r="9" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="137" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="114"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="114"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
     </row>
     <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="114"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="137"/>
     </row>
     <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="114"/>
-      <c r="F13" s="114"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
     </row>
     <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
     </row>
     <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="114"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4647,21 +5144,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -15513,7 +16010,7 @@
     <col min="6" max="6" width="11.33203125" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="10" width="20" style="134" customWidth="1"/>
+    <col min="9" max="10" width="20" style="129" customWidth="1"/>
     <col min="11" max="11" width="20" style="45" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
@@ -15522,24 +16019,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="136" t="s">
         <v>687</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
@@ -15563,19 +16060,19 @@
       <c r="G3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="121" t="s">
+      <c r="H3" s="117" t="s">
         <v>75</v>
       </c>
-      <c r="I3" s="132" t="s">
+      <c r="I3" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="132" t="s">
+      <c r="J3" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="121" t="s">
         <v>634</v>
       </c>
-      <c r="L3" s="125" t="s">
+      <c r="L3" s="120" t="s">
         <v>76</v>
       </c>
       <c r="M3" s="2" t="s">
@@ -15592,27 +16089,27 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="138" t="s">
         <v>688</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
     </row>
     <row r="5" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="114" t="s">
         <v>81</v>
       </c>
       <c r="B5" s="8"/>
@@ -15631,13 +16128,13 @@
       <c r="G5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="140" t="s">
+      <c r="H5" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M5" s="14" t="s">
@@ -15678,19 +16175,19 @@
       <c r="G7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="133" t="s">
+      <c r="H7" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="128" t="s">
         <v>911</v>
       </c>
-      <c r="J7" s="133" t="s">
+      <c r="J7" s="128" t="s">
         <v>910</v>
       </c>
-      <c r="K7" s="127" t="s">
+      <c r="K7" s="122" t="s">
         <v>911</v>
       </c>
-      <c r="L7" s="140" t="s">
+      <c r="L7" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M7" s="14" t="s">
@@ -15726,19 +16223,19 @@
       <c r="G8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="133" t="s">
+      <c r="H8" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="128" t="s">
         <v>912</v>
       </c>
-      <c r="J8" s="133" t="s">
+      <c r="J8" s="128" t="s">
         <v>913</v>
       </c>
-      <c r="K8" s="127" t="s">
+      <c r="K8" s="122" t="s">
         <v>910</v>
       </c>
-      <c r="L8" s="140" t="s">
+      <c r="L8" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M8" s="14" t="s">
@@ -15774,13 +16271,13 @@
       <c r="G9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="140" t="s">
+      <c r="H9" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M9" s="14" t="s">
@@ -15818,16 +16315,16 @@
       <c r="G10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="123" t="s">
+      <c r="H10" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="135" t="s">
+      <c r="J10" s="130" t="s">
         <v>914</v>
       </c>
-      <c r="K10" s="128" t="s">
+      <c r="K10" s="123" t="s">
         <v>913</v>
       </c>
-      <c r="L10" s="140" t="s">
+      <c r="L10" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M10" s="14" t="s">
@@ -15844,24 +16341,24 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="116" t="s">
+      <c r="A11" s="138" t="s">
         <v>689</v>
       </c>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="116"/>
-      <c r="N11" s="116"/>
-      <c r="O11" s="116"/>
-      <c r="P11" s="116"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138"/>
+      <c r="L11" s="138"/>
+      <c r="M11" s="138"/>
+      <c r="N11" s="138"/>
+      <c r="O11" s="138"/>
+      <c r="P11" s="138"/>
     </row>
     <row r="12" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
@@ -15883,16 +16380,16 @@
       <c r="G12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="133" t="s">
+      <c r="H12" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="128" t="s">
         <v>913</v>
       </c>
-      <c r="K12" s="127" t="s">
+      <c r="K12" s="122" t="s">
         <v>910</v>
       </c>
-      <c r="L12" s="140" t="s">
+      <c r="L12" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M12" s="14" t="s">
@@ -15928,13 +16425,13 @@
       <c r="G13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="133"/>
-      <c r="J13" s="133"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="140" t="s">
+      <c r="H13" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M13" s="14" t="s">
@@ -15970,17 +16467,17 @@
       <c r="G14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="133"/>
-      <c r="J14" s="133" t="s">
+      <c r="H14" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="128"/>
+      <c r="J14" s="128" t="s">
         <v>912</v>
       </c>
-      <c r="K14" s="127" t="s">
+      <c r="K14" s="122" t="s">
         <v>910</v>
       </c>
-      <c r="L14" s="140" t="s">
+      <c r="L14" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M14" s="14" t="s">
@@ -15995,7 +16492,7 @@
       <c r="P14" s="8"/>
     </row>
     <row r="15" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="117" t="s">
+      <c r="A15" s="114" t="s">
         <v>113</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -16016,13 +16513,13 @@
       <c r="G15" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="127"/>
-      <c r="L15" s="140" t="s">
+      <c r="H15" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M15" s="14" t="s">
@@ -16037,7 +16534,7 @@
       <c r="P15" s="8"/>
     </row>
     <row r="16" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="117" t="s">
+      <c r="A16" s="114" t="s">
         <v>118</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -16058,13 +16555,13 @@
       <c r="G16" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="133"/>
-      <c r="J16" s="133"/>
-      <c r="K16" s="127"/>
-      <c r="L16" s="140" t="s">
+      <c r="H16" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M16" s="14" t="s">
@@ -16079,24 +16576,24 @@
       <c r="P16" s="8"/>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="138" t="s">
         <v>690</v>
       </c>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="116"/>
-      <c r="I17" s="116"/>
-      <c r="J17" s="116"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="116"/>
-      <c r="N17" s="116"/>
-      <c r="O17" s="116"/>
-      <c r="P17" s="116"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="138"/>
+      <c r="L17" s="138"/>
+      <c r="M17" s="138"/>
+      <c r="N17" s="138"/>
+      <c r="O17" s="138"/>
+      <c r="P17" s="138"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
@@ -16120,13 +16617,13 @@
       <c r="G18" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" s="133"/>
-      <c r="J18" s="133"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="140" t="s">
+      <c r="H18" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M18" s="14" t="s">
@@ -16162,13 +16659,13 @@
       <c r="G19" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="133"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="127"/>
-      <c r="L19" s="140" t="s">
+      <c r="H19" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M19" s="14" t="s">
@@ -16206,13 +16703,13 @@
       <c r="G20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="123" t="s">
+      <c r="H20" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="135"/>
-      <c r="J20" s="135"/>
-      <c r="K20" s="128"/>
-      <c r="L20" s="140" t="s">
+      <c r="I20" s="130"/>
+      <c r="J20" s="130"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M20" s="14" t="s">
@@ -16248,17 +16745,17 @@
       <c r="G21" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="133" t="s">
+      <c r="H21" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="128" t="s">
         <v>913</v>
       </c>
-      <c r="J21" s="133"/>
-      <c r="K21" s="127" t="s">
+      <c r="J21" s="128"/>
+      <c r="K21" s="122" t="s">
         <v>916</v>
       </c>
-      <c r="L21" s="140" t="s">
+      <c r="L21" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M21" s="14" t="s">
@@ -16296,13 +16793,13 @@
       <c r="G22" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" s="133"/>
-      <c r="J22" s="133"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="140" t="s">
+      <c r="H22" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="128"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M22" s="14" t="s">
@@ -16340,13 +16837,13 @@
       <c r="G23" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="133"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="140" t="s">
+      <c r="H23" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M23" s="14" t="s">
@@ -16382,13 +16879,13 @@
       <c r="G24" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H24" s="124" t="s">
+      <c r="H24" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="I24" s="136"/>
-      <c r="J24" s="136"/>
-      <c r="K24" s="129"/>
-      <c r="L24" s="140" t="s">
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M24" s="14" t="s">
@@ -16422,13 +16919,13 @@
       <c r="G25" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I25" s="133"/>
-      <c r="J25" s="133"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="140" t="s">
+      <c r="H25" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="128"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M25" s="14" t="s">
@@ -16462,13 +16959,13 @@
       <c r="G26" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="133"/>
-      <c r="J26" s="133"/>
-      <c r="K26" s="127"/>
-      <c r="L26" s="140" t="s">
+      <c r="H26" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="128"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M26" s="14" t="s">
@@ -16506,13 +17003,13 @@
       <c r="G27" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="127"/>
-      <c r="L27" s="140" t="s">
+      <c r="H27" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="128"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M27" s="14" t="s">
@@ -16550,13 +17047,13 @@
       <c r="G28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H28" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I28" s="133"/>
-      <c r="J28" s="133"/>
-      <c r="K28" s="127"/>
-      <c r="L28" s="140" t="s">
+      <c r="H28" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" s="128"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M28" s="14" t="s">
@@ -16571,24 +17068,24 @@
       <c r="P28" s="8"/>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="116" t="s">
+      <c r="A29" s="138" t="s">
         <v>691</v>
       </c>
-      <c r="B29" s="116"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="116"/>
-      <c r="N29" s="116"/>
-      <c r="O29" s="116"/>
-      <c r="P29" s="116"/>
+      <c r="B29" s="138"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="138"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="138"/>
     </row>
     <row r="30" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="75" t="s">
@@ -16612,17 +17109,17 @@
       <c r="G30" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I30" s="133" t="s">
+      <c r="H30" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" s="128" t="s">
         <v>913</v>
       </c>
-      <c r="J30" s="118" t="s">
+      <c r="J30" s="139" t="s">
         <v>918</v>
       </c>
-      <c r="K30" s="119"/>
-      <c r="L30" s="140" t="s">
+      <c r="K30" s="140"/>
+      <c r="L30" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M30" s="14" t="s">
@@ -16656,19 +17153,19 @@
       <c r="G31" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" s="133" t="s">
+      <c r="H31" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="128" t="s">
         <v>913</v>
       </c>
-      <c r="J31" s="133" t="s">
+      <c r="J31" s="128" t="s">
         <v>914</v>
       </c>
-      <c r="K31" s="127" t="s">
+      <c r="K31" s="122" t="s">
         <v>910</v>
       </c>
-      <c r="L31" s="140" t="s">
+      <c r="L31" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M31" s="14" t="s">
@@ -16702,17 +17199,17 @@
       <c r="G32" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32" s="133"/>
-      <c r="J32" s="133" t="s">
+      <c r="H32" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="128"/>
+      <c r="J32" s="128" t="s">
         <v>914</v>
       </c>
-      <c r="K32" s="127" t="s">
+      <c r="K32" s="122" t="s">
         <v>910</v>
       </c>
-      <c r="L32" s="140" t="s">
+      <c r="L32" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M32" s="14" t="s">
@@ -16746,14 +17243,14 @@
       <c r="G33" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J33" s="139" t="s">
+      <c r="H33" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="134" t="s">
         <v>154</v>
       </c>
-      <c r="K33" s="127"/>
-      <c r="L33" s="140" t="s">
+      <c r="K33" s="122"/>
+      <c r="L33" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M33" s="14" t="s">
@@ -16768,27 +17265,27 @@
       <c r="P33" s="8"/>
     </row>
     <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="116" t="s">
+      <c r="A34" s="138" t="s">
         <v>692</v>
       </c>
-      <c r="B34" s="116"/>
-      <c r="C34" s="116"/>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="116"/>
-      <c r="M34" s="116"/>
-      <c r="N34" s="116"/>
-      <c r="O34" s="116"/>
-      <c r="P34" s="116"/>
+      <c r="B34" s="138"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="138"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="138"/>
+      <c r="G34" s="138"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="138"/>
+      <c r="J34" s="138"/>
+      <c r="K34" s="138"/>
+      <c r="L34" s="138"/>
+      <c r="M34" s="138"/>
+      <c r="N34" s="138"/>
+      <c r="O34" s="138"/>
+      <c r="P34" s="138"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="120" t="s">
+      <c r="A35" s="116" t="s">
         <v>162</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -16809,13 +17306,13 @@
       <c r="G35" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H35" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" s="133"/>
-      <c r="J35" s="133"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="140" t="s">
+      <c r="H35" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="122"/>
+      <c r="L35" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M35" s="14" t="s">
@@ -16832,7 +17329,7 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="120" t="s">
+      <c r="A36" s="116" t="s">
         <v>168</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -16853,13 +17350,13 @@
       <c r="G36" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H36" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I36" s="133"/>
-      <c r="J36" s="133"/>
-      <c r="K36" s="127"/>
-      <c r="L36" s="140" t="s">
+      <c r="H36" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="135" t="s">
         <v>115</v>
       </c>
       <c r="M36" s="14" t="s">
@@ -16897,17 +17394,17 @@
       <c r="G37" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H37" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37" s="133" t="s">
+      <c r="H37" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37" s="128" t="s">
         <v>914</v>
       </c>
-      <c r="J37" s="133"/>
-      <c r="K37" s="127" t="s">
+      <c r="J37" s="128"/>
+      <c r="K37" s="122" t="s">
         <v>911</v>
       </c>
-      <c r="L37" s="140" t="s">
+      <c r="L37" s="135" t="s">
         <v>115</v>
       </c>
       <c r="M37" s="14" t="s">
@@ -16924,27 +17421,27 @@
       </c>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="116" t="s">
+      <c r="A38" s="138" t="s">
         <v>693</v>
       </c>
-      <c r="B38" s="116"/>
-      <c r="C38" s="116"/>
-      <c r="D38" s="116"/>
-      <c r="E38" s="116"/>
-      <c r="F38" s="116"/>
-      <c r="G38" s="116"/>
-      <c r="H38" s="116"/>
-      <c r="I38" s="116"/>
-      <c r="J38" s="116"/>
-      <c r="K38" s="116"/>
-      <c r="L38" s="116"/>
-      <c r="M38" s="116"/>
-      <c r="N38" s="116"/>
-      <c r="O38" s="116"/>
-      <c r="P38" s="116"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="138"/>
+      <c r="K38" s="138"/>
+      <c r="L38" s="138"/>
+      <c r="M38" s="138"/>
+      <c r="N38" s="138"/>
+      <c r="O38" s="138"/>
+      <c r="P38" s="138"/>
     </row>
     <row r="39" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="117" t="s">
+      <c r="A39" s="114" t="s">
         <v>177</v>
       </c>
       <c r="B39" s="76" t="s">
@@ -16965,13 +17462,13 @@
       <c r="G39" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H39" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" s="133"/>
-      <c r="J39" s="133"/>
-      <c r="K39" s="127"/>
-      <c r="L39" s="140" t="s">
+      <c r="H39" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="128"/>
+      <c r="J39" s="128"/>
+      <c r="K39" s="122"/>
+      <c r="L39" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M39" s="14" t="s">
@@ -16988,7 +17485,7 @@
       </c>
     </row>
     <row r="40" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="117" t="s">
+      <c r="A40" s="114" t="s">
         <v>182</v>
       </c>
       <c r="B40" s="8"/>
@@ -17007,13 +17504,13 @@
       <c r="G40" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H40" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I40" s="133"/>
-      <c r="J40" s="133"/>
-      <c r="K40" s="127"/>
-      <c r="L40" s="140" t="s">
+      <c r="H40" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="128"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="122"/>
+      <c r="L40" s="135" t="s">
         <v>84</v>
       </c>
       <c r="M40" s="14" t="s">
@@ -17047,13 +17544,13 @@
       <c r="G41" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41" s="133"/>
-      <c r="J41" s="133"/>
-      <c r="K41" s="127"/>
-      <c r="L41" s="140" t="s">
+      <c r="H41" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" s="128"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="122"/>
+      <c r="L41" s="135" t="s">
         <v>92</v>
       </c>
       <c r="M41" s="14" t="s">
@@ -17089,13 +17586,13 @@
       <c r="G42" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="133"/>
-      <c r="J42" s="133"/>
-      <c r="K42" s="127"/>
-      <c r="L42" s="140"/>
+      <c r="H42" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" s="128"/>
+      <c r="J42" s="128"/>
+      <c r="K42" s="122"/>
+      <c r="L42" s="135"/>
       <c r="M42" s="14" t="s">
         <v>188</v>
       </c>
@@ -17113,9 +17610,9 @@
       <c r="A44" s="36" t="s">
         <v>723</v>
       </c>
-      <c r="I44" s="137"/>
-      <c r="J44" s="137"/>
-      <c r="K44" s="130"/>
+      <c r="I44" s="132"/>
+      <c r="J44" s="132"/>
+      <c r="K44" s="125"/>
     </row>
     <row r="45" spans="1:16" s="54" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="53"/>
@@ -17125,9 +17622,9 @@
       <c r="D45" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="131"/>
+      <c r="I45" s="133"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="126"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B46" s="38"/>
@@ -17151,6 +17648,9 @@
       </c>
     </row>
     <row r="48" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="25" t="s">
+        <v>177</v>
+      </c>
       <c r="B48" s="71">
         <v>46223</v>
       </c>
@@ -17171,7 +17671,9 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="38"/>
+      <c r="B50" s="38" t="s">
+        <v>920</v>
+      </c>
       <c r="C50" s="68" t="s">
         <v>861</v>
       </c>
@@ -17180,7 +17682,9 @@
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="38"/>
+      <c r="B51" s="142" t="s">
+        <v>921</v>
+      </c>
       <c r="C51" s="45" t="s">
         <v>832</v>
       </c>
@@ -17189,7 +17693,9 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B52" s="38"/>
+      <c r="B52" s="38" t="s">
+        <v>922</v>
+      </c>
       <c r="C52" s="45" t="s">
         <v>836</v>
       </c>
@@ -17198,7 +17704,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B53" s="38" t="s">
+      <c r="B53" s="141" t="s">
         <v>860</v>
       </c>
       <c r="C53" s="57" t="s">
@@ -17210,7 +17716,9 @@
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B54" s="38"/>
+      <c r="B54" s="38" t="s">
+        <v>923</v>
+      </c>
       <c r="C54" s="57" t="s">
         <v>758</v>
       </c>
@@ -17222,9 +17730,9 @@
       <c r="A55" s="53"/>
       <c r="C55" s="55"/>
       <c r="D55" s="55"/>
-      <c r="I55" s="138"/>
-      <c r="J55" s="138"/>
-      <c r="K55" s="131"/>
+      <c r="I55" s="133"/>
+      <c r="J55" s="133"/>
+      <c r="K55" s="126"/>
     </row>
     <row r="56" spans="1:11" s="54" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="53"/>
@@ -17233,12 +17741,14 @@
         <v>805</v>
       </c>
       <c r="D56" s="86"/>
-      <c r="I56" s="138"/>
-      <c r="J56" s="138"/>
-      <c r="K56" s="131"/>
+      <c r="I56" s="133"/>
+      <c r="J56" s="133"/>
+      <c r="K56" s="126"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B57" s="38"/>
+      <c r="B57" s="141" t="s">
+        <v>919</v>
+      </c>
       <c r="C57" s="57" t="s">
         <v>785</v>
       </c>
@@ -17259,7 +17769,7 @@
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B59" s="38" t="s">
+      <c r="B59" s="141" t="s">
         <v>845</v>
       </c>
       <c r="C59" s="57" t="s">
@@ -17273,6 +17783,9 @@
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="25" t="s">
+        <v>924</v>
+      </c>
       <c r="B60" s="71">
         <v>46223</v>
       </c>
@@ -17280,8 +17793,14 @@
         <v>837</v>
       </c>
       <c r="D60" s="56"/>
+      <c r="E60" s="143" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="61" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="25" t="s">
+        <v>925</v>
+      </c>
       <c r="B61" s="71">
         <v>46223</v>
       </c>
@@ -17289,6 +17808,7 @@
         <v>838</v>
       </c>
       <c r="D61" s="56"/>
+      <c r="E61" s="143"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B62" s="71"/>
@@ -17303,7 +17823,7 @@
       <c r="D63" s="82"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B64" s="38" t="s">
+      <c r="B64" s="141" t="s">
         <v>844</v>
       </c>
       <c r="C64" s="57" t="s">
@@ -17313,8 +17833,8 @@
         <v>749</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="38" t="s">
+    <row r="65" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B65" s="141" t="s">
         <v>846</v>
       </c>
       <c r="C65" s="57" t="s">
@@ -17324,20 +17844,20 @@
         <v>749</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B66" s="71"/>
       <c r="C66" s="27"/>
       <c r="D66" s="26"/>
     </row>
-    <row r="67" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B67" s="38"/>
       <c r="C67" s="94" t="s">
         <v>804</v>
       </c>
       <c r="D67" s="82"/>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="38" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B68" s="141" t="s">
         <v>847</v>
       </c>
       <c r="C68" s="56" t="s">
@@ -17350,8 +17870,8 @@
         <v>830</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="38" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B69" s="141" t="s">
         <v>848</v>
       </c>
       <c r="C69" s="45" t="s">
@@ -17361,8 +17881,8 @@
         <v>724</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="38" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B70" s="141" t="s">
         <v>849</v>
       </c>
       <c r="C70" s="45" t="s">
@@ -17375,8 +17895,8 @@
         <v>850</v>
       </c>
     </row>
-    <row r="71" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B71" s="38" t="s">
+    <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B71" s="141" t="s">
         <v>851</v>
       </c>
       <c r="C71" s="57" t="s">
@@ -17389,8 +17909,8 @@
         <v>850</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="38" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="141" t="s">
         <v>852</v>
       </c>
       <c r="C72" s="45" t="s">
@@ -17403,8 +17923,8 @@
         <v>850</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="38" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B73" s="141" t="s">
         <v>853</v>
       </c>
       <c r="C73" s="45" t="s">
@@ -17414,7 +17934,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B74" s="38"/>
       <c r="C74" s="45" t="s">
         <v>730</v>
@@ -17423,7 +17943,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B75" s="38"/>
       <c r="C75" s="45" t="s">
         <v>751</v>
@@ -17432,7 +17952,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B76" s="38"/>
       <c r="C76" s="57" t="s">
         <v>773</v>
@@ -17441,14 +17961,17 @@
         <v>724</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B77" s="38"/>
       <c r="C77" s="94" t="s">
         <v>808</v>
       </c>
       <c r="D77" s="82"/>
     </row>
-    <row r="78" spans="2:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A78" s="25" t="s">
+        <v>927</v>
+      </c>
       <c r="B78" s="38" t="s">
         <v>854</v>
       </c>
@@ -17459,8 +17982,8 @@
         <v>737</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B79" s="38" t="s">
+    <row r="79" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B79" s="141" t="s">
         <v>855</v>
       </c>
       <c r="C79" s="57" t="s">
@@ -17473,8 +17996,8 @@
         <v>850</v>
       </c>
     </row>
-    <row r="80" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B80" s="38" t="s">
+    <row r="80" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B80" s="141" t="s">
         <v>856</v>
       </c>
       <c r="C80" s="57" t="s">
@@ -17488,7 +18011,7 @@
       </c>
     </row>
     <row r="81" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B81" s="38" t="s">
+      <c r="B81" s="141" t="s">
         <v>857</v>
       </c>
       <c r="C81" s="57" t="s">
@@ -17502,7 +18025,7 @@
       </c>
     </row>
     <row r="82" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B82" s="38" t="s">
+      <c r="B82" s="141" t="s">
         <v>858</v>
       </c>
       <c r="C82" s="57" t="s">
@@ -17516,7 +18039,7 @@
       </c>
     </row>
     <row r="83" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B83" s="38" t="s">
+      <c r="B83" s="141" t="s">
         <v>859</v>
       </c>
       <c r="C83" s="57" t="s">
@@ -17539,7 +18062,8 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C57:D83">
     <sortCondition ref="D57:D83"/>
   </sortState>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="E60:E61"/>
     <mergeCell ref="A34:P34"/>
     <mergeCell ref="A38:P38"/>
     <mergeCell ref="A1:P1"/>
@@ -17549,6 +18073,7 @@
     <mergeCell ref="A29:P29"/>
     <mergeCell ref="J30:K30"/>
   </mergeCells>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -17556,7 +18081,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -17573,21 +18098,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="136" t="s">
         <v>694</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -17631,21 +18156,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="138" t="s">
         <v>695</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
     </row>
     <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -17966,21 +18491,21 @@
       <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="116" t="s">
+      <c r="A13" s="138" t="s">
         <v>696</v>
       </c>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
-      <c r="M13" s="116"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="138"/>
+      <c r="K13" s="138"/>
+      <c r="L13" s="138"/>
+      <c r="M13" s="138"/>
     </row>
     <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
@@ -18024,21 +18549,21 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="138" t="s">
         <v>697</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
@@ -18164,21 +18689,21 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="116" t="s">
+      <c r="A19" s="138" t="s">
         <v>698</v>
       </c>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="116"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="138"/>
+      <c r="K19" s="138"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="138"/>
     </row>
     <row r="20" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -18218,21 +18743,21 @@
       <c r="M20" s="8"/>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="116" t="s">
+      <c r="A21" s="138" t="s">
         <v>699</v>
       </c>
-      <c r="B21" s="116"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="116"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="138"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="138"/>
+      <c r="K21" s="138"/>
+      <c r="L21" s="138"/>
+      <c r="M21" s="138"/>
     </row>
     <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
@@ -18468,21 +18993,21 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="116" t="s">
+      <c r="A28" s="138" t="s">
         <v>700</v>
       </c>
-      <c r="B28" s="116"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="116"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="138"/>
     </row>
     <row r="29" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
@@ -19988,21 +20513,21 @@
       </c>
     </row>
     <row r="67" spans="1:13" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="116" t="s">
+      <c r="A67" s="138" t="s">
         <v>701</v>
       </c>
-      <c r="B67" s="116"/>
-      <c r="C67" s="116"/>
-      <c r="D67" s="116"/>
-      <c r="E67" s="116"/>
-      <c r="F67" s="116"/>
-      <c r="G67" s="116"/>
-      <c r="H67" s="116"/>
-      <c r="I67" s="116"/>
-      <c r="J67" s="116"/>
-      <c r="K67" s="116"/>
-      <c r="L67" s="116"/>
-      <c r="M67" s="116"/>
+      <c r="B67" s="138"/>
+      <c r="C67" s="138"/>
+      <c r="D67" s="138"/>
+      <c r="E67" s="138"/>
+      <c r="F67" s="138"/>
+      <c r="G67" s="138"/>
+      <c r="H67" s="138"/>
+      <c r="I67" s="138"/>
+      <c r="J67" s="138"/>
+      <c r="K67" s="138"/>
+      <c r="L67" s="138"/>
+      <c r="M67" s="138"/>
     </row>
     <row r="68" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
@@ -20188,7 +20713,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C81" s="65" t="s">
         <v>769</v>
       </c>
@@ -20196,7 +20721,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C82" s="65" t="s">
         <v>874</v>
       </c>
@@ -20204,7 +20729,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C83" s="65" t="s">
         <v>760</v>
       </c>
@@ -20212,7 +20737,10 @@
         <v>757</v>
       </c>
     </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>928</v>
+      </c>
       <c r="B84" s="73" t="s">
         <v>833</v>
       </c>
@@ -20223,7 +20751,10 @@
         <v>862</v>
       </c>
     </row>
-    <row r="85" spans="2:4" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>929</v>
+      </c>
       <c r="C85" s="65" t="s">
         <v>873</v>
       </c>
@@ -20231,13 +20762,13 @@
         <v>757</v>
       </c>
     </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C86" s="83" t="s">
         <v>825</v>
       </c>
       <c r="D86" s="84"/>
     </row>
-    <row r="87" spans="2:4" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="C87" s="65" t="s">
         <v>784</v>
       </c>
@@ -20245,13 +20776,17 @@
         <v>772</v>
       </c>
     </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="144"/>
       <c r="C88" s="83" t="s">
         <v>811</v>
       </c>
       <c r="D88" s="84"/>
     </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="145" t="s">
+        <v>930</v>
+      </c>
       <c r="B89" s="73" t="s">
         <v>842</v>
       </c>
@@ -20260,13 +20795,19 @@
       </c>
       <c r="D89" s="56"/>
     </row>
-    <row r="90" spans="2:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A90" s="145" t="s">
+        <v>931</v>
+      </c>
       <c r="C90" s="65" t="s">
         <v>843</v>
       </c>
       <c r="D90" s="56"/>
     </row>
-    <row r="91" spans="2:4" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A91" s="145" t="s">
+        <v>932</v>
+      </c>
       <c r="B91" s="73" t="s">
         <v>892</v>
       </c>
@@ -20277,14 +20818,17 @@
         <v>811</v>
       </c>
     </row>
-    <row r="92" spans="2:4" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="73"/>
       <c r="C92" s="65" t="s">
         <v>896</v>
       </c>
       <c r="D92" s="56"/>
     </row>
-    <row r="93" spans="2:4" ht="66" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A93" s="145" t="s">
+        <v>933</v>
+      </c>
       <c r="C93" s="65" t="s">
         <v>894</v>
       </c>
@@ -20292,7 +20836,10 @@
         <v>761</v>
       </c>
     </row>
-    <row r="94" spans="2:4" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A94" s="145" t="s">
+        <v>934</v>
+      </c>
       <c r="B94" s="91">
         <v>46232</v>
       </c>
@@ -20303,7 +20850,10 @@
         <v>761</v>
       </c>
     </row>
-    <row r="95" spans="2:4" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="145" t="s">
+        <v>935</v>
+      </c>
       <c r="C95" s="65" t="s">
         <v>764</v>
       </c>
@@ -20311,7 +20861,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B96" s="74" t="s">
         <v>833</v>
       </c>
@@ -20320,7 +20870,10 @@
       </c>
       <c r="D96" s="85"/>
     </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="145" t="s">
+        <v>942</v>
+      </c>
       <c r="C97" s="65" t="s">
         <v>834</v>
       </c>
@@ -20328,18 +20881,51 @@
         <v>908</v>
       </c>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C98" s="109" t="s">
         <v>899</v>
       </c>
       <c r="D98" s="112"/>
     </row>
-    <row r="99" spans="3:4" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A99" s="145" t="s">
+        <v>943</v>
+      </c>
       <c r="C99" s="110" t="s">
         <v>906</v>
       </c>
       <c r="D99" s="111" t="s">
         <v>907</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C114" s="146" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="C115" s="147" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="C116" s="147" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="C117" s="147" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="C118" s="147" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="C119" s="147" t="s">
+        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -20356,6 +20942,7 @@
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A19:M19"/>
   </mergeCells>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -20410,6 +20997,11 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="113"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="148" t="s">
+        <v>956</v>
+      </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="113"/>
@@ -20439,21 +21031,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="136" t="s">
         <v>702</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -20497,21 +21089,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="138" t="s">
         <v>703</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
     </row>
     <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -20555,21 +21147,21 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="116" t="s">
+      <c r="A6" s="138" t="s">
         <v>704</v>
       </c>
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
+      <c r="B6" s="138"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="138"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="M6" s="138"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
@@ -20652,21 +21244,21 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="116" t="s">
+      <c r="A9" s="138" t="s">
         <v>705</v>
       </c>
-      <c r="B9" s="116"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="116"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="116"/>
-      <c r="H9" s="116"/>
-      <c r="I9" s="116"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="116"/>
-      <c r="L9" s="116"/>
-      <c r="M9" s="116"/>
+      <c r="B9" s="138"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="138"/>
+      <c r="K9" s="138"/>
+      <c r="L9" s="138"/>
+      <c r="M9" s="138"/>
     </row>
     <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
@@ -20823,21 +21415,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="138" t="s">
         <v>706</v>
       </c>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="116"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="138"/>
     </row>
     <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
@@ -20877,21 +21469,21 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="138" t="s">
         <v>707</v>
       </c>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="116"/>
-      <c r="H16" s="116"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="116"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
+      <c r="M16" s="138"/>
     </row>
     <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -21091,21 +21683,21 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="116" t="s">
+      <c r="A22" s="138" t="s">
         <v>708</v>
       </c>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="116"/>
+      <c r="B22" s="138"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="138"/>
     </row>
     <row r="23" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
@@ -21403,21 +21995,21 @@
       <c r="M30" s="8"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="116" t="s">
+      <c r="A31" s="138" t="s">
         <v>709</v>
       </c>
-      <c r="B31" s="116"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116"/>
-      <c r="L31" s="116"/>
-      <c r="M31" s="116"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="138"/>
     </row>
     <row r="32" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
@@ -21533,21 +22125,21 @@
       <c r="M34" s="8"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="116" t="s">
+      <c r="A35" s="138" t="s">
         <v>710</v>
       </c>
-      <c r="B35" s="116"/>
-      <c r="C35" s="116"/>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="116"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="116"/>
-      <c r="L35" s="116"/>
-      <c r="M35" s="116"/>
+      <c r="B35" s="138"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="138"/>
+      <c r="J35" s="138"/>
+      <c r="K35" s="138"/>
+      <c r="L35" s="138"/>
+      <c r="M35" s="138"/>
     </row>
     <row r="36" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
@@ -22224,21 +22816,21 @@
       <c r="M53" s="8"/>
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="116" t="s">
+      <c r="A54" s="138" t="s">
         <v>711</v>
       </c>
-      <c r="B54" s="116"/>
-      <c r="C54" s="116"/>
-      <c r="D54" s="116"/>
-      <c r="E54" s="116"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="116"/>
-      <c r="H54" s="116"/>
-      <c r="I54" s="116"/>
-      <c r="J54" s="116"/>
-      <c r="K54" s="116"/>
-      <c r="L54" s="116"/>
-      <c r="M54" s="116"/>
+      <c r="B54" s="138"/>
+      <c r="C54" s="138"/>
+      <c r="D54" s="138"/>
+      <c r="E54" s="138"/>
+      <c r="F54" s="138"/>
+      <c r="G54" s="138"/>
+      <c r="H54" s="138"/>
+      <c r="I54" s="138"/>
+      <c r="J54" s="138"/>
+      <c r="K54" s="138"/>
+      <c r="L54" s="138"/>
+      <c r="M54" s="138"/>
     </row>
     <row r="55" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
@@ -22278,21 +22870,21 @@
       <c r="M55" s="8"/>
     </row>
     <row r="56" spans="1:13" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="116" t="s">
+      <c r="A56" s="138" t="s">
         <v>712</v>
       </c>
-      <c r="B56" s="116"/>
-      <c r="C56" s="116"/>
-      <c r="D56" s="116"/>
-      <c r="E56" s="116"/>
-      <c r="F56" s="116"/>
-      <c r="G56" s="116"/>
-      <c r="H56" s="116"/>
-      <c r="I56" s="116"/>
-      <c r="J56" s="116"/>
-      <c r="K56" s="116"/>
-      <c r="L56" s="116"/>
-      <c r="M56" s="116"/>
+      <c r="B56" s="138"/>
+      <c r="C56" s="138"/>
+      <c r="D56" s="138"/>
+      <c r="E56" s="138"/>
+      <c r="F56" s="138"/>
+      <c r="G56" s="138"/>
+      <c r="H56" s="138"/>
+      <c r="I56" s="138"/>
+      <c r="J56" s="138"/>
+      <c r="K56" s="138"/>
+      <c r="L56" s="138"/>
+      <c r="M56" s="138"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
@@ -22360,6 +22952,9 @@
       </c>
     </row>
     <row r="61" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>950</v>
+      </c>
       <c r="C61" s="45" t="s">
         <v>770</v>
       </c>
@@ -22369,6 +22964,9 @@
       <c r="E61" s="38"/>
     </row>
     <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>951</v>
+      </c>
       <c r="C62" s="45" t="s">
         <v>828</v>
       </c>
@@ -22387,6 +22985,9 @@
       <c r="E63" s="38"/>
     </row>
     <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>952</v>
+      </c>
       <c r="C64" s="57" t="s">
         <v>774</v>
       </c>
@@ -22396,6 +22997,9 @@
       <c r="E64" s="38"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>953</v>
+      </c>
       <c r="C65" s="45" t="s">
         <v>775</v>
       </c>
@@ -22412,6 +23016,9 @@
       <c r="E66" s="38"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>954</v>
+      </c>
       <c r="C67" s="69" t="s">
         <v>779</v>
       </c>
@@ -22430,6 +23037,9 @@
       <c r="E68" s="38"/>
     </row>
     <row r="69" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>955</v>
+      </c>
       <c r="C69" s="57" t="s">
         <v>788</v>
       </c>
@@ -22454,17 +23064,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A14:M14"/>
     <mergeCell ref="A56:M56"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A31:M31"/>
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A54:M54"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A14:M14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D65" r:id="rId1" xr:uid="{5086776A-0A7E-4AED-AE41-2F854BC2FEE7}"/>
@@ -22493,21 +23103,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="136" t="s">
         <v>713</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -22551,21 +23161,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="138" t="s">
         <v>714</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
     </row>
     <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -22981,21 +23591,21 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="138" t="s">
         <v>715</v>
       </c>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="116"/>
-      <c r="H16" s="116"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="116"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
+      <c r="M16" s="138"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -23745,21 +24355,21 @@
       <c r="M36" s="8"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="116" t="s">
+      <c r="A37" s="138" t="s">
         <v>716</v>
       </c>
-      <c r="B37" s="116"/>
-      <c r="C37" s="116"/>
-      <c r="D37" s="116"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="116"/>
-      <c r="H37" s="116"/>
-      <c r="I37" s="116"/>
-      <c r="J37" s="116"/>
-      <c r="K37" s="116"/>
-      <c r="L37" s="116"/>
-      <c r="M37" s="116"/>
+      <c r="B37" s="138"/>
+      <c r="C37" s="138"/>
+      <c r="D37" s="138"/>
+      <c r="E37" s="138"/>
+      <c r="F37" s="138"/>
+      <c r="G37" s="138"/>
+      <c r="H37" s="138"/>
+      <c r="I37" s="138"/>
+      <c r="J37" s="138"/>
+      <c r="K37" s="138"/>
+      <c r="L37" s="138"/>
+      <c r="M37" s="138"/>
     </row>
     <row r="38" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
@@ -24397,21 +25007,21 @@
       <c r="M54" s="8"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="116" t="s">
+      <c r="A55" s="138" t="s">
         <v>717</v>
       </c>
-      <c r="B55" s="116"/>
-      <c r="C55" s="116"/>
-      <c r="D55" s="116"/>
-      <c r="E55" s="116"/>
-      <c r="F55" s="116"/>
-      <c r="G55" s="116"/>
-      <c r="H55" s="116"/>
-      <c r="I55" s="116"/>
-      <c r="J55" s="116"/>
-      <c r="K55" s="116"/>
-      <c r="L55" s="116"/>
-      <c r="M55" s="116"/>
+      <c r="B55" s="138"/>
+      <c r="C55" s="138"/>
+      <c r="D55" s="138"/>
+      <c r="E55" s="138"/>
+      <c r="F55" s="138"/>
+      <c r="G55" s="138"/>
+      <c r="H55" s="138"/>
+      <c r="I55" s="138"/>
+      <c r="J55" s="138"/>
+      <c r="K55" s="138"/>
+      <c r="L55" s="138"/>
+      <c r="M55" s="138"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
@@ -25461,6 +26071,9 @@
       <c r="D84" s="85"/>
     </row>
     <row r="85" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>944</v>
+      </c>
       <c r="C85" s="65" t="s">
         <v>782</v>
       </c>
@@ -25473,6 +26086,9 @@
       <c r="D86" s="100"/>
     </row>
     <row r="87" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>945</v>
+      </c>
       <c r="C87" s="65" t="s">
         <v>885</v>
       </c>
@@ -25485,12 +26101,18 @@
       <c r="D88" s="99"/>
     </row>
     <row r="89" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>946</v>
+      </c>
       <c r="C89" s="65" t="s">
         <v>883</v>
       </c>
       <c r="D89" s="45"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>947</v>
+      </c>
       <c r="C90" s="65" t="s">
         <v>889</v>
       </c>
@@ -25502,6 +26124,9 @@
       <c r="D91" s="103"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>948</v>
+      </c>
       <c r="C92" s="65" t="s">
         <v>777</v>
       </c>
@@ -25514,6 +26139,9 @@
       <c r="D93" s="107"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>949</v>
+      </c>
       <c r="C94" s="65" t="s">
         <v>898</v>
       </c>
@@ -25551,21 +26179,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="136" t="s">
         <v>718</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -25609,21 +26237,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="138" t="s">
         <v>719</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">

--- a/data/Caboodle_Backlog_by_Module (1).xlsx
+++ b/data/Caboodle_Backlog_by_Module (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\My Code\Caboodle\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F34D0CE-F834-454D-BE04-D1A6C803F118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D58180-1730-401F-96FB-B3FB5E7A8D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -3614,8 +3614,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Segoe UI"/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3923,7 +3924,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4246,11 +4247,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4261,24 +4280,12 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
@@ -4438,9 +4445,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1044015</xdr:colOff>
+      <xdr:colOff>1047825</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>93405</xdr:rowOff>
+      <xdr:rowOff>97215</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4482,7 +4489,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>20062</xdr:colOff>
+      <xdr:colOff>16252</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>379094</xdr:rowOff>
     </xdr:to>
@@ -4528,7 +4535,7 @@
       <xdr:col>34</xdr:col>
       <xdr:colOff>532286</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>285026</xdr:rowOff>
+      <xdr:rowOff>288836</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4926,197 +4933,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
     </row>
     <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
     </row>
     <row r="4" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="137" t="s">
+      <c r="B4" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="137"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
+      <c r="B5" s="143"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="137"/>
-      <c r="C6" s="137"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="137"/>
+      <c r="B6" s="143"/>
+      <c r="C6" s="143"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
     </row>
     <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
     </row>
     <row r="8" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="137"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="137"/>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143"/>
     </row>
     <row r="9" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="137" t="s">
+      <c r="B9" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="137"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
+      <c r="C9" s="143"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="143"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="137"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="137"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
+      <c r="B10" s="143"/>
+      <c r="C10" s="143"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
     </row>
     <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="137"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
+      <c r="C12" s="143"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="143"/>
     </row>
     <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="137" t="s">
+      <c r="B13" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
     </row>
     <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="137" t="s">
+      <c r="B14" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="137"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="137" t="s">
+      <c r="B15" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
     </row>
     <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="137"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="137"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5144,21 +5151,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -16019,24 +16026,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="144" t="s">
         <v>687</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
@@ -16089,24 +16096,24 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="146" t="s">
         <v>688</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="138"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
+      <c r="O4" s="146"/>
+      <c r="P4" s="146"/>
     </row>
     <row r="5" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="114" t="s">
@@ -16341,24 +16348,24 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="138" t="s">
+      <c r="A11" s="146" t="s">
         <v>689</v>
       </c>
-      <c r="B11" s="138"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="138"/>
-      <c r="L11" s="138"/>
-      <c r="M11" s="138"/>
-      <c r="N11" s="138"/>
-      <c r="O11" s="138"/>
-      <c r="P11" s="138"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="146"/>
     </row>
     <row r="12" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
@@ -16576,24 +16583,24 @@
       <c r="P16" s="8"/>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="138" t="s">
+      <c r="A17" s="146" t="s">
         <v>690</v>
       </c>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="138"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="138"/>
-      <c r="M17" s="138"/>
-      <c r="N17" s="138"/>
-      <c r="O17" s="138"/>
-      <c r="P17" s="138"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="146"/>
+      <c r="H17" s="146"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="146"/>
+      <c r="L17" s="146"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="146"/>
+      <c r="O17" s="146"/>
+      <c r="P17" s="146"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
@@ -17068,24 +17075,24 @@
       <c r="P28" s="8"/>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="138" t="s">
+      <c r="A29" s="146" t="s">
         <v>691</v>
       </c>
-      <c r="B29" s="138"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="138"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="138"/>
-      <c r="M29" s="138"/>
-      <c r="N29" s="138"/>
-      <c r="O29" s="138"/>
-      <c r="P29" s="138"/>
+      <c r="B29" s="146"/>
+      <c r="C29" s="146"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="146"/>
+      <c r="H29" s="146"/>
+      <c r="I29" s="146"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="146"/>
+      <c r="L29" s="146"/>
+      <c r="M29" s="146"/>
+      <c r="N29" s="146"/>
+      <c r="O29" s="146"/>
+      <c r="P29" s="146"/>
     </row>
     <row r="30" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="75" t="s">
@@ -17115,10 +17122,10 @@
       <c r="I30" s="128" t="s">
         <v>913</v>
       </c>
-      <c r="J30" s="139" t="s">
+      <c r="J30" s="147" t="s">
         <v>918</v>
       </c>
-      <c r="K30" s="140"/>
+      <c r="K30" s="148"/>
       <c r="L30" s="135" t="s">
         <v>84</v>
       </c>
@@ -17265,24 +17272,24 @@
       <c r="P33" s="8"/>
     </row>
     <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="138" t="s">
+      <c r="A34" s="146" t="s">
         <v>692</v>
       </c>
-      <c r="B34" s="138"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="138"/>
-      <c r="J34" s="138"/>
-      <c r="K34" s="138"/>
-      <c r="L34" s="138"/>
-      <c r="M34" s="138"/>
-      <c r="N34" s="138"/>
-      <c r="O34" s="138"/>
-      <c r="P34" s="138"/>
+      <c r="B34" s="146"/>
+      <c r="C34" s="146"/>
+      <c r="D34" s="146"/>
+      <c r="E34" s="146"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="146"/>
+      <c r="H34" s="146"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="146"/>
+      <c r="K34" s="146"/>
+      <c r="L34" s="146"/>
+      <c r="M34" s="146"/>
+      <c r="N34" s="146"/>
+      <c r="O34" s="146"/>
+      <c r="P34" s="146"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="116" t="s">
@@ -17421,24 +17428,24 @@
       </c>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="138" t="s">
+      <c r="A38" s="146" t="s">
         <v>693</v>
       </c>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="138"/>
-      <c r="N38" s="138"/>
-      <c r="O38" s="138"/>
-      <c r="P38" s="138"/>
+      <c r="B38" s="146"/>
+      <c r="C38" s="146"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="146"/>
+      <c r="H38" s="146"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="146"/>
+      <c r="K38" s="146"/>
+      <c r="L38" s="146"/>
+      <c r="M38" s="146"/>
+      <c r="N38" s="146"/>
+      <c r="O38" s="146"/>
+      <c r="P38" s="146"/>
     </row>
     <row r="39" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="114" t="s">
@@ -17682,7 +17689,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="142" t="s">
+      <c r="B51" s="137" t="s">
         <v>921</v>
       </c>
       <c r="C51" s="45" t="s">
@@ -17704,7 +17711,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B53" s="141" t="s">
+      <c r="B53" s="136" t="s">
         <v>860</v>
       </c>
       <c r="C53" s="57" t="s">
@@ -17746,7 +17753,7 @@
       <c r="K56" s="126"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B57" s="141" t="s">
+      <c r="B57" s="136" t="s">
         <v>919</v>
       </c>
       <c r="C57" s="57" t="s">
@@ -17769,7 +17776,7 @@
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B59" s="141" t="s">
+      <c r="B59" s="136" t="s">
         <v>845</v>
       </c>
       <c r="C59" s="57" t="s">
@@ -17793,7 +17800,7 @@
         <v>837</v>
       </c>
       <c r="D60" s="56"/>
-      <c r="E60" s="143" t="s">
+      <c r="E60" s="145" t="s">
         <v>926</v>
       </c>
     </row>
@@ -17808,7 +17815,7 @@
         <v>838</v>
       </c>
       <c r="D61" s="56"/>
-      <c r="E61" s="143"/>
+      <c r="E61" s="145"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B62" s="71"/>
@@ -17823,7 +17830,7 @@
       <c r="D63" s="82"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B64" s="141" t="s">
+      <c r="B64" s="136" t="s">
         <v>844</v>
       </c>
       <c r="C64" s="57" t="s">
@@ -17834,7 +17841,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="141" t="s">
+      <c r="B65" s="136" t="s">
         <v>846</v>
       </c>
       <c r="C65" s="57" t="s">
@@ -17857,7 +17864,7 @@
       <c r="D67" s="82"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="141" t="s">
+      <c r="B68" s="136" t="s">
         <v>847</v>
       </c>
       <c r="C68" s="56" t="s">
@@ -17871,7 +17878,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="141" t="s">
+      <c r="B69" s="136" t="s">
         <v>848</v>
       </c>
       <c r="C69" s="45" t="s">
@@ -17882,7 +17889,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="141" t="s">
+      <c r="B70" s="136" t="s">
         <v>849</v>
       </c>
       <c r="C70" s="45" t="s">
@@ -17896,7 +17903,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B71" s="141" t="s">
+      <c r="B71" s="136" t="s">
         <v>851</v>
       </c>
       <c r="C71" s="57" t="s">
@@ -17910,7 +17917,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="141" t="s">
+      <c r="B72" s="136" t="s">
         <v>852</v>
       </c>
       <c r="C72" s="45" t="s">
@@ -17924,7 +17931,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="141" t="s">
+      <c r="B73" s="136" t="s">
         <v>853</v>
       </c>
       <c r="C73" s="45" t="s">
@@ -17983,7 +17990,7 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B79" s="141" t="s">
+      <c r="B79" s="136" t="s">
         <v>855</v>
       </c>
       <c r="C79" s="57" t="s">
@@ -17997,7 +18004,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B80" s="141" t="s">
+      <c r="B80" s="136" t="s">
         <v>856</v>
       </c>
       <c r="C80" s="57" t="s">
@@ -18011,7 +18018,7 @@
       </c>
     </row>
     <row r="81" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B81" s="141" t="s">
+      <c r="B81" s="136" t="s">
         <v>857</v>
       </c>
       <c r="C81" s="57" t="s">
@@ -18025,7 +18032,7 @@
       </c>
     </row>
     <row r="82" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B82" s="141" t="s">
+      <c r="B82" s="136" t="s">
         <v>858</v>
       </c>
       <c r="C82" s="57" t="s">
@@ -18039,7 +18046,7 @@
       </c>
     </row>
     <row r="83" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B83" s="141" t="s">
+      <c r="B83" s="136" t="s">
         <v>859</v>
       </c>
       <c r="C83" s="57" t="s">
@@ -18098,21 +18105,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="144" t="s">
         <v>694</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -18156,21 +18163,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="146" t="s">
         <v>695</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
     </row>
     <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -18491,21 +18498,21 @@
       <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="138" t="s">
+      <c r="A13" s="146" t="s">
         <v>696</v>
       </c>
-      <c r="B13" s="138"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
-      <c r="J13" s="138"/>
-      <c r="K13" s="138"/>
-      <c r="L13" s="138"/>
-      <c r="M13" s="138"/>
+      <c r="B13" s="146"/>
+      <c r="C13" s="146"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="146"/>
+      <c r="G13" s="146"/>
+      <c r="H13" s="146"/>
+      <c r="I13" s="146"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="146"/>
+      <c r="M13" s="146"/>
     </row>
     <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
@@ -18549,21 +18556,21 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="146" t="s">
         <v>697</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="146"/>
+      <c r="H15" s="146"/>
+      <c r="I15" s="146"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="146"/>
+      <c r="M15" s="146"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
@@ -18689,21 +18696,21 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="138" t="s">
+      <c r="A19" s="146" t="s">
         <v>698</v>
       </c>
-      <c r="B19" s="138"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="138"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="138"/>
-      <c r="K19" s="138"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="138"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="146"/>
+      <c r="E19" s="146"/>
+      <c r="F19" s="146"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="146"/>
+      <c r="I19" s="146"/>
+      <c r="J19" s="146"/>
+      <c r="K19" s="146"/>
+      <c r="L19" s="146"/>
+      <c r="M19" s="146"/>
     </row>
     <row r="20" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -18743,21 +18750,21 @@
       <c r="M20" s="8"/>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="138" t="s">
+      <c r="A21" s="146" t="s">
         <v>699</v>
       </c>
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="138"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="138"/>
-      <c r="M21" s="138"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="146"/>
+      <c r="H21" s="146"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="146"/>
+      <c r="L21" s="146"/>
+      <c r="M21" s="146"/>
     </row>
     <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
@@ -18993,21 +19000,21 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="138" t="s">
+      <c r="A28" s="146" t="s">
         <v>700</v>
       </c>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="138"/>
-      <c r="M28" s="138"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="146"/>
+      <c r="D28" s="146"/>
+      <c r="E28" s="146"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="146"/>
+      <c r="H28" s="146"/>
+      <c r="I28" s="146"/>
+      <c r="J28" s="146"/>
+      <c r="K28" s="146"/>
+      <c r="L28" s="146"/>
+      <c r="M28" s="146"/>
     </row>
     <row r="29" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
@@ -20513,21 +20520,21 @@
       </c>
     </row>
     <row r="67" spans="1:13" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="138" t="s">
+      <c r="A67" s="146" t="s">
         <v>701</v>
       </c>
-      <c r="B67" s="138"/>
-      <c r="C67" s="138"/>
-      <c r="D67" s="138"/>
-      <c r="E67" s="138"/>
-      <c r="F67" s="138"/>
-      <c r="G67" s="138"/>
-      <c r="H67" s="138"/>
-      <c r="I67" s="138"/>
-      <c r="J67" s="138"/>
-      <c r="K67" s="138"/>
-      <c r="L67" s="138"/>
-      <c r="M67" s="138"/>
+      <c r="B67" s="146"/>
+      <c r="C67" s="146"/>
+      <c r="D67" s="146"/>
+      <c r="E67" s="146"/>
+      <c r="F67" s="146"/>
+      <c r="G67" s="146"/>
+      <c r="H67" s="146"/>
+      <c r="I67" s="146"/>
+      <c r="J67" s="146"/>
+      <c r="K67" s="146"/>
+      <c r="L67" s="146"/>
+      <c r="M67" s="146"/>
     </row>
     <row r="68" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
@@ -20706,34 +20713,34 @@
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C80" s="65" t="s">
+      <c r="C80" s="149" t="s">
         <v>756</v>
       </c>
-      <c r="D80" s="56" t="s">
+      <c r="D80" s="150" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C81" s="65" t="s">
+      <c r="C81" s="149" t="s">
         <v>769</v>
       </c>
-      <c r="D81" s="56" t="s">
+      <c r="D81" s="150" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C82" s="65" t="s">
+      <c r="C82" s="149" t="s">
         <v>874</v>
       </c>
-      <c r="D82" s="56" t="s">
+      <c r="D82" s="150" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C83" s="65" t="s">
+      <c r="C83" s="149" t="s">
         <v>760</v>
       </c>
-      <c r="D83" s="56" t="s">
+      <c r="D83" s="150" t="s">
         <v>757</v>
       </c>
     </row>
@@ -20777,14 +20784,14 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="144"/>
+      <c r="A88" s="138"/>
       <c r="C88" s="83" t="s">
         <v>811</v>
       </c>
       <c r="D88" s="84"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="145" t="s">
+      <c r="A89" s="139" t="s">
         <v>930</v>
       </c>
       <c r="B89" s="73" t="s">
@@ -20796,7 +20803,7 @@
       <c r="D89" s="56"/>
     </row>
     <row r="90" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="145" t="s">
+      <c r="A90" s="139" t="s">
         <v>931</v>
       </c>
       <c r="C90" s="65" t="s">
@@ -20805,7 +20812,7 @@
       <c r="D90" s="56"/>
     </row>
     <row r="91" spans="1:4" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A91" s="145" t="s">
+      <c r="A91" s="139" t="s">
         <v>932</v>
       </c>
       <c r="B91" s="73" t="s">
@@ -20826,7 +20833,7 @@
       <c r="D92" s="56"/>
     </row>
     <row r="93" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A93" s="145" t="s">
+      <c r="A93" s="139" t="s">
         <v>933</v>
       </c>
       <c r="C93" s="65" t="s">
@@ -20837,7 +20844,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A94" s="145" t="s">
+      <c r="A94" s="139" t="s">
         <v>934</v>
       </c>
       <c r="B94" s="91">
@@ -20851,7 +20858,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="145" t="s">
+      <c r="A95" s="139" t="s">
         <v>935</v>
       </c>
       <c r="C95" s="65" t="s">
@@ -20871,7 +20878,7 @@
       <c r="D96" s="85"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="145" t="s">
+      <c r="A97" s="139" t="s">
         <v>942</v>
       </c>
       <c r="C97" s="65" t="s">
@@ -20888,7 +20895,7 @@
       <c r="D98" s="112"/>
     </row>
     <row r="99" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A99" s="145" t="s">
+      <c r="A99" s="139" t="s">
         <v>943</v>
       </c>
       <c r="C99" s="110" t="s">
@@ -20899,32 +20906,32 @@
       </c>
     </row>
     <row r="114" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C114" s="146" t="s">
+      <c r="C114" s="140" t="s">
         <v>936</v>
       </c>
     </row>
     <row r="115" spans="3:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="C115" s="147" t="s">
+      <c r="C115" s="141" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="116" spans="3:3" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="C116" s="147" t="s">
+      <c r="C116" s="141" t="s">
         <v>938</v>
       </c>
     </row>
     <row r="117" spans="3:3" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="C117" s="147" t="s">
+      <c r="C117" s="141" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="118" spans="3:3" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="C118" s="147" t="s">
+      <c r="C118" s="141" t="s">
         <v>940</v>
       </c>
     </row>
     <row r="119" spans="3:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="C119" s="147" t="s">
+      <c r="C119" s="141" t="s">
         <v>941</v>
       </c>
     </row>
@@ -20999,7 +21006,7 @@
       <c r="A36" s="113"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="148" t="s">
+      <c r="A38" s="142" t="s">
         <v>956</v>
       </c>
     </row>
@@ -21031,21 +21038,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="144" t="s">
         <v>702</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -21089,21 +21096,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="146" t="s">
         <v>703</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
     </row>
     <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -21147,21 +21154,21 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="138" t="s">
+      <c r="A6" s="146" t="s">
         <v>704</v>
       </c>
-      <c r="B6" s="138"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="138"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="138"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="146"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
@@ -21244,21 +21251,21 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="138" t="s">
+      <c r="A9" s="146" t="s">
         <v>705</v>
       </c>
-      <c r="B9" s="138"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="138"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
-      <c r="M9" s="138"/>
+      <c r="B9" s="146"/>
+      <c r="C9" s="146"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="146"/>
+      <c r="F9" s="146"/>
+      <c r="G9" s="146"/>
+      <c r="H9" s="146"/>
+      <c r="I9" s="146"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="146"/>
+      <c r="L9" s="146"/>
+      <c r="M9" s="146"/>
     </row>
     <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
@@ -21415,21 +21422,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="138" t="s">
+      <c r="A14" s="146" t="s">
         <v>706</v>
       </c>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
-      <c r="M14" s="138"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="146"/>
+      <c r="I14" s="146"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="146"/>
+      <c r="M14" s="146"/>
     </row>
     <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
@@ -21469,21 +21476,21 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="138" t="s">
+      <c r="A16" s="146" t="s">
         <v>707</v>
       </c>
-      <c r="B16" s="138"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="138"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138"/>
-      <c r="M16" s="138"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="146"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="146"/>
+      <c r="M16" s="146"/>
     </row>
     <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -21683,21 +21690,21 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="138" t="s">
+      <c r="A22" s="146" t="s">
         <v>708</v>
       </c>
-      <c r="B22" s="138"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138"/>
-      <c r="M22" s="138"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="146"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="146"/>
+      <c r="G22" s="146"/>
+      <c r="H22" s="146"/>
+      <c r="I22" s="146"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="146"/>
+      <c r="L22" s="146"/>
+      <c r="M22" s="146"/>
     </row>
     <row r="23" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
@@ -21995,21 +22002,21 @@
       <c r="M30" s="8"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="138" t="s">
+      <c r="A31" s="146" t="s">
         <v>709</v>
       </c>
-      <c r="B31" s="138"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="138"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="138"/>
-      <c r="M31" s="138"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="146"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="146"/>
+      <c r="G31" s="146"/>
+      <c r="H31" s="146"/>
+      <c r="I31" s="146"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="146"/>
+      <c r="L31" s="146"/>
+      <c r="M31" s="146"/>
     </row>
     <row r="32" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
@@ -22125,21 +22132,21 @@
       <c r="M34" s="8"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="138" t="s">
+      <c r="A35" s="146" t="s">
         <v>710</v>
       </c>
-      <c r="B35" s="138"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138"/>
-      <c r="K35" s="138"/>
-      <c r="L35" s="138"/>
-      <c r="M35" s="138"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="146"/>
+      <c r="G35" s="146"/>
+      <c r="H35" s="146"/>
+      <c r="I35" s="146"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="146"/>
+      <c r="L35" s="146"/>
+      <c r="M35" s="146"/>
     </row>
     <row r="36" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
@@ -22816,21 +22823,21 @@
       <c r="M53" s="8"/>
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="138" t="s">
+      <c r="A54" s="146" t="s">
         <v>711</v>
       </c>
-      <c r="B54" s="138"/>
-      <c r="C54" s="138"/>
-      <c r="D54" s="138"/>
-      <c r="E54" s="138"/>
-      <c r="F54" s="138"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="138"/>
-      <c r="I54" s="138"/>
-      <c r="J54" s="138"/>
-      <c r="K54" s="138"/>
-      <c r="L54" s="138"/>
-      <c r="M54" s="138"/>
+      <c r="B54" s="146"/>
+      <c r="C54" s="146"/>
+      <c r="D54" s="146"/>
+      <c r="E54" s="146"/>
+      <c r="F54" s="146"/>
+      <c r="G54" s="146"/>
+      <c r="H54" s="146"/>
+      <c r="I54" s="146"/>
+      <c r="J54" s="146"/>
+      <c r="K54" s="146"/>
+      <c r="L54" s="146"/>
+      <c r="M54" s="146"/>
     </row>
     <row r="55" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
@@ -22870,21 +22877,21 @@
       <c r="M55" s="8"/>
     </row>
     <row r="56" spans="1:13" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="138" t="s">
+      <c r="A56" s="146" t="s">
         <v>712</v>
       </c>
-      <c r="B56" s="138"/>
-      <c r="C56" s="138"/>
-      <c r="D56" s="138"/>
-      <c r="E56" s="138"/>
-      <c r="F56" s="138"/>
-      <c r="G56" s="138"/>
-      <c r="H56" s="138"/>
-      <c r="I56" s="138"/>
-      <c r="J56" s="138"/>
-      <c r="K56" s="138"/>
-      <c r="L56" s="138"/>
-      <c r="M56" s="138"/>
+      <c r="B56" s="146"/>
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="146"/>
+      <c r="H56" s="146"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="146"/>
+      <c r="K56" s="146"/>
+      <c r="L56" s="146"/>
+      <c r="M56" s="146"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
@@ -23064,17 +23071,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A14:M14"/>
     <mergeCell ref="A56:M56"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A31:M31"/>
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A54:M54"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A14:M14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D65" r:id="rId1" xr:uid="{5086776A-0A7E-4AED-AE41-2F854BC2FEE7}"/>
@@ -23103,21 +23110,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="144" t="s">
         <v>713</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -23161,21 +23168,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="146" t="s">
         <v>714</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
     </row>
     <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -23591,21 +23598,21 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="138" t="s">
+      <c r="A16" s="146" t="s">
         <v>715</v>
       </c>
-      <c r="B16" s="138"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="138"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138"/>
-      <c r="M16" s="138"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="146"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="146"/>
+      <c r="M16" s="146"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -24355,21 +24362,21 @@
       <c r="M36" s="8"/>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="138" t="s">
+      <c r="A37" s="146" t="s">
         <v>716</v>
       </c>
-      <c r="B37" s="138"/>
-      <c r="C37" s="138"/>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="138"/>
-      <c r="K37" s="138"/>
-      <c r="L37" s="138"/>
-      <c r="M37" s="138"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="146"/>
+      <c r="D37" s="146"/>
+      <c r="E37" s="146"/>
+      <c r="F37" s="146"/>
+      <c r="G37" s="146"/>
+      <c r="H37" s="146"/>
+      <c r="I37" s="146"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
+      <c r="L37" s="146"/>
+      <c r="M37" s="146"/>
     </row>
     <row r="38" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
@@ -25007,21 +25014,21 @@
       <c r="M54" s="8"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="138" t="s">
+      <c r="A55" s="146" t="s">
         <v>717</v>
       </c>
-      <c r="B55" s="138"/>
-      <c r="C55" s="138"/>
-      <c r="D55" s="138"/>
-      <c r="E55" s="138"/>
-      <c r="F55" s="138"/>
-      <c r="G55" s="138"/>
-      <c r="H55" s="138"/>
-      <c r="I55" s="138"/>
-      <c r="J55" s="138"/>
-      <c r="K55" s="138"/>
-      <c r="L55" s="138"/>
-      <c r="M55" s="138"/>
+      <c r="B55" s="146"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="146"/>
+      <c r="G55" s="146"/>
+      <c r="H55" s="146"/>
+      <c r="I55" s="146"/>
+      <c r="J55" s="146"/>
+      <c r="K55" s="146"/>
+      <c r="L55" s="146"/>
+      <c r="M55" s="146"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
@@ -26179,21 +26186,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="144" t="s">
         <v>718</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -26237,21 +26244,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="146" t="s">
         <v>719</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
